--- a/leads/out/pa-trades-leads.xlsx
+++ b/leads/out/pa-trades-leads.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$P$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$Q$90</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P90"/>
+  <dimension ref="A1:Q90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -494,9 +494,10 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -567,15 +568,20 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>Source Notes</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Retrieved</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Source ID</t>
         </is>
@@ -628,17 +634,18 @@
         </is>
       </c>
       <c r="M2" s="5" t="n"/>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N2" s="2" t="n"/>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>614da4054996d900012c34a2</t>
         </is>
@@ -691,17 +698,18 @@
         </is>
       </c>
       <c r="M3" s="5" t="n"/>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
         <is>
           <t>54a1a2bf74686942d363ac03</t>
         </is>
@@ -754,17 +762,18 @@
         </is>
       </c>
       <c r="M4" s="5" t="n"/>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N4" s="2" t="n"/>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>54a11bd969702d8ed4256200</t>
         </is>
@@ -817,17 +826,18 @@
         </is>
       </c>
       <c r="M5" s="5" t="n"/>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N5" s="2" t="n"/>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>57c4f7eda6da986aaa172238</t>
         </is>
@@ -880,17 +890,18 @@
         </is>
       </c>
       <c r="M6" s="5" t="n"/>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N6" s="2" t="n"/>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>5e5610acf74c260001f7d303</t>
         </is>
@@ -943,17 +954,18 @@
         </is>
       </c>
       <c r="M7" s="5" t="n"/>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N7" s="2" t="n"/>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>5fd85c81c0cf980001cf01c9</t>
         </is>
@@ -1006,17 +1018,18 @@
         </is>
       </c>
       <c r="M8" s="5" t="n"/>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>62eb4841004d24000161dae3</t>
         </is>
@@ -1067,15 +1080,20 @@
       <c r="M9" s="5" t="n"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Apollo reports state=Pennsylvania but raw_address and +44 phone indicate Limerick, Ireland. Geography filter will pass this incorrectly.</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>556d54fb7369641266ffeb00</t>
         </is>
@@ -1128,17 +1146,18 @@
         </is>
       </c>
       <c r="M10" s="5" t="n"/>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N10" s="2" t="n"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>5f49df2bf15fd000014be47f</t>
         </is>
@@ -1193,15 +1212,20 @@
       <c r="M11" s="5" t="n"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Distributor, not a contractor.</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>61b6f541117cfd00a48bc4c2</t>
         </is>
@@ -1254,17 +1278,18 @@
         </is>
       </c>
       <c r="M12" s="5" t="n"/>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N12" s="2" t="n"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>5f4827ea7a32a000011996c7</t>
         </is>
@@ -1317,17 +1342,18 @@
         </is>
       </c>
       <c r="M13" s="5" t="n"/>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N13" s="2" t="n"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>6437c5a0b0185e01b39eb62e</t>
         </is>
@@ -1380,17 +1406,18 @@
         </is>
       </c>
       <c r="M14" s="5" t="n"/>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N14" s="2" t="n"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>636ce79ea839d300a34c2beb</t>
         </is>
@@ -1443,17 +1470,18 @@
         </is>
       </c>
       <c r="M15" s="5" t="n"/>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N15" s="2" t="n"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>65e2e8d09db56401c6b45eea</t>
         </is>
@@ -1504,15 +1532,20 @@
       <c r="M16" s="5" t="n"/>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Queried gillece.com; Apollo matched a different org record (id 54a1364b..., no primary_domain) than the lookup result (id 6336c0bd..., 'Gillece Services').</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>54a1364b69702d46f0051401</t>
         </is>
@@ -1567,15 +1600,20 @@
       <c r="M17" s="5" t="n"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Manufacturer of concrete fiber, not a contractor. Owned by The Heritage Group.</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>54a1289b69702d9548e62201</t>
         </is>
@@ -1630,15 +1668,20 @@
       <c r="M18" s="5" t="n"/>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Concrete supplier. Owned by Gray Concrete Construction.</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>6726fb136893d600010ae1c5</t>
         </is>
@@ -1691,17 +1734,18 @@
         </is>
       </c>
       <c r="M19" s="5" t="n"/>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N19" s="2" t="n"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>54a11cf469702d9d7e62e300</t>
         </is>
@@ -1754,17 +1798,18 @@
         </is>
       </c>
       <c r="M20" s="5" t="n"/>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N20" s="2" t="n"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>556dc3937369641258da8301</t>
         </is>
@@ -1817,17 +1862,18 @@
         </is>
       </c>
       <c r="M21" s="5" t="n"/>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N21" s="2" t="n"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>6129a94cc7406400016e8192</t>
         </is>
@@ -1880,17 +1926,18 @@
         </is>
       </c>
       <c r="M22" s="5" t="n"/>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N22" s="2" t="n"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>5d096a28f651257f55823650</t>
         </is>
@@ -1943,17 +1990,18 @@
         </is>
       </c>
       <c r="M23" s="5" t="n"/>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N23" s="2" t="n"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>55ef0a72f3e5bb285000281c</t>
         </is>
@@ -2008,15 +2056,20 @@
       <c r="M24" s="5" t="n"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Apollo's short_description describes a Minnesota injection-molding firm, not this PA HVAC/refrigeration contractor. Description field is unreliable for this record.</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>5c1ec7d4f651259b6e1f4b5b</t>
         </is>
@@ -2069,17 +2122,18 @@
         </is>
       </c>
       <c r="M25" s="5" t="n"/>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N25" s="2" t="n"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>664c381c0302770001727f9d</t>
         </is>
@@ -2132,17 +2186,18 @@
         </is>
       </c>
       <c r="M26" s="5" t="n"/>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N26" s="2" t="n"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>56de964bf3e5bb706e000fe4</t>
         </is>
@@ -2195,17 +2250,18 @@
         </is>
       </c>
       <c r="M27" s="5" t="n"/>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N27" s="2" t="n"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>5f485faab495f8000111eb37</t>
         </is>
@@ -2258,17 +2314,18 @@
         </is>
       </c>
       <c r="M28" s="5" t="n"/>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N28" s="2" t="n"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>56e29dfef3e5bb18dd00148d</t>
         </is>
@@ -2321,17 +2378,18 @@
         </is>
       </c>
       <c r="M29" s="5" t="n"/>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N29" s="2" t="n"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>5da6eb5884afb000019f805d</t>
         </is>
@@ -2384,17 +2442,18 @@
         </is>
       </c>
       <c r="M30" s="5" t="n"/>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N30" s="2" t="n"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>67284c4962f46c0001d23e6e</t>
         </is>
@@ -2447,17 +2506,18 @@
         </is>
       </c>
       <c r="M31" s="5" t="n"/>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>55eb8c91f3e5bb13700002e4</t>
         </is>
@@ -2510,17 +2570,18 @@
         </is>
       </c>
       <c r="M32" s="5" t="n"/>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N32" s="2" t="n"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>54a1d1b674686945fa9b7e13</t>
         </is>
@@ -2573,17 +2634,18 @@
         </is>
       </c>
       <c r="M33" s="5" t="n"/>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N33" s="2" t="n"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
         <is>
           <t>5da361a4e53eb80001767204</t>
         </is>
@@ -2636,17 +2698,18 @@
         </is>
       </c>
       <c r="M34" s="5" t="n"/>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N34" s="2" t="n"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>5a9e305fa6da98d96643c97b</t>
         </is>
@@ -2699,17 +2762,18 @@
         </is>
       </c>
       <c r="M35" s="5" t="n"/>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N35" s="2" t="n"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>54a138e269702d2bfdc91300</t>
         </is>
@@ -2762,17 +2826,18 @@
         </is>
       </c>
       <c r="M36" s="5" t="n"/>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N36" s="2" t="n"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
         <is>
           <t>5fcb2475439c2e00016b5ac4</t>
         </is>
@@ -2825,17 +2890,18 @@
         </is>
       </c>
       <c r="M37" s="5" t="n"/>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N37" s="2" t="n"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>5ed9e7a99be60d0001d993ce</t>
         </is>
@@ -2888,17 +2954,18 @@
         </is>
       </c>
       <c r="M38" s="5" t="n"/>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N38" s="2" t="n"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
         <is>
           <t>59bb9db8a6da9824096d7912</t>
         </is>
@@ -2951,17 +3018,18 @@
         </is>
       </c>
       <c r="M39" s="5" t="n"/>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
         <is>
           <t>5eda3c0b7a685300010b8862</t>
         </is>
@@ -3014,17 +3082,18 @@
         </is>
       </c>
       <c r="M40" s="5" t="n"/>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N40" s="2" t="n"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
         <is>
           <t>54a1354669702d3cbbbea600</t>
         </is>
@@ -3077,17 +3146,18 @@
         </is>
       </c>
       <c r="M41" s="5" t="n"/>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N41" s="2" t="n"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
         <is>
           <t>61e6d805df00f100dae67383</t>
         </is>
@@ -3140,17 +3210,18 @@
         </is>
       </c>
       <c r="M42" s="5" t="n"/>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N42" s="2" t="n"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
         <is>
           <t>54a19a07746869586086e200</t>
         </is>
@@ -3205,15 +3276,20 @@
       <c r="M43" s="5" t="n"/>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Shares phone with Gray Concrete 2 Go (sister company, same number).</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
         <is>
           <t>5500c2ba7369646159214300</t>
         </is>
@@ -3266,17 +3342,18 @@
         </is>
       </c>
       <c r="M44" s="5" t="n"/>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N44" s="2" t="n"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
         <is>
           <t>54a1c0f974686945fa29ff0d</t>
         </is>
@@ -3329,17 +3406,18 @@
         </is>
       </c>
       <c r="M45" s="5" t="n"/>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N45" s="2" t="n"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
         <is>
           <t>55f432b7f3e5bb1e190069c8</t>
         </is>
@@ -3394,15 +3472,20 @@
       <c r="M46" s="5" t="n"/>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Owned by HomeServe UK; ultimate parent Brookfield. Not independent.</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
         <is>
           <t>54a1284569702d9548b1f900</t>
         </is>
@@ -3455,17 +3538,18 @@
         </is>
       </c>
       <c r="M47" s="5" t="n"/>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N47" s="2" t="n"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
         <is>
           <t>5ed11ee3cd850a000199d744</t>
         </is>
@@ -3520,15 +3604,20 @@
       <c r="M48" s="5" t="n"/>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Valve manufacturer (brand of ThermOmegaTech), not a contractor.</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
         <is>
           <t>5e559ec4e04e960001855c43</t>
         </is>
@@ -3581,17 +3670,18 @@
         </is>
       </c>
       <c r="M49" s="5" t="n"/>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N49" s="2" t="n"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
         <is>
           <t>5a9e6e05a6da98d9664553e2</t>
         </is>
@@ -3644,17 +3734,18 @@
         </is>
       </c>
       <c r="M50" s="5" t="n"/>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N50" s="2" t="n"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
         <is>
           <t>5da61aa4d84d9e0001386a2e</t>
         </is>
@@ -3707,17 +3798,18 @@
         </is>
       </c>
       <c r="M51" s="5" t="n"/>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N51" s="2" t="n"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
         <is>
           <t>670b293e7d492300015414c5</t>
         </is>
@@ -3772,15 +3864,20 @@
       <c r="M52" s="5" t="n"/>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Building-materials retailer, not primarily a contractor.</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
         <is>
           <t>5da4510d03c66e00011876be</t>
         </is>
@@ -3833,17 +3930,18 @@
         </is>
       </c>
       <c r="M53" s="5" t="n"/>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N53" s="2" t="n"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
         <is>
           <t>56de9c76f3e5bb7076001141</t>
         </is>
@@ -3898,15 +3996,20 @@
       <c r="M54" s="5" t="n"/>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Trade association, not a contractor.</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
         <is>
           <t>63c3b92eee04d800010feb2f</t>
         </is>
@@ -3959,17 +4062,18 @@
         </is>
       </c>
       <c r="M55" s="5" t="n"/>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N55" s="2" t="n"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
         <is>
           <t>5e58e614a5b0780001f1d42f</t>
         </is>
@@ -4022,17 +4126,18 @@
         </is>
       </c>
       <c r="M56" s="5" t="n"/>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N56" s="2" t="n"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
         <is>
           <t>64164711385f42000186c58c</t>
         </is>
@@ -4085,17 +4190,18 @@
         </is>
       </c>
       <c r="M57" s="5" t="n"/>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N57" s="2" t="n"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
         <is>
           <t>54a1b72b74686949e76d8f0a</t>
         </is>
@@ -4148,17 +4254,18 @@
         </is>
       </c>
       <c r="M58" s="5" t="n"/>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N58" s="2" t="n"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
         <is>
           <t>55699f177369642598ac6800</t>
         </is>
@@ -4211,17 +4318,18 @@
         </is>
       </c>
       <c r="M59" s="5" t="n"/>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N59" s="2" t="n"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
         <is>
           <t>5500cdc973696460f4427800</t>
         </is>
@@ -4274,17 +4382,18 @@
         </is>
       </c>
       <c r="M60" s="5" t="n"/>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N60" s="2" t="n"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
         <is>
           <t>5fc9cc7976b13600019d82f8</t>
         </is>
@@ -4337,17 +4446,18 @@
         </is>
       </c>
       <c r="M61" s="5" t="n"/>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N61" s="2" t="n"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
         <is>
           <t>67991fc100c3d201b0dc6241</t>
         </is>
@@ -4400,17 +4510,18 @@
         </is>
       </c>
       <c r="M62" s="5" t="n"/>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N62" s="2" t="n"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
         <is>
           <t>54a1340c69702d2db4795200</t>
         </is>
@@ -4463,17 +4574,18 @@
         </is>
       </c>
       <c r="M63" s="5" t="n"/>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N63" s="2" t="n"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
         <is>
           <t>556d65eb736964122f1efe00</t>
         </is>
@@ -4526,17 +4638,18 @@
         </is>
       </c>
       <c r="M64" s="5" t="n"/>
-      <c r="N64" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N64" s="2" t="n"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
         <is>
           <t>6612993ae6ca0d0007d0673c</t>
         </is>
@@ -4589,17 +4702,18 @@
         </is>
       </c>
       <c r="M65" s="5" t="n"/>
-      <c r="N65" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N65" s="2" t="n"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
         <is>
           <t>54a1392669702de5b3a11500</t>
         </is>
@@ -4652,17 +4766,18 @@
         </is>
       </c>
       <c r="M66" s="5" t="n"/>
-      <c r="N66" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N66" s="2" t="n"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
         <is>
           <t>54a1353669702d48e2536e00</t>
         </is>
@@ -4715,17 +4830,18 @@
         </is>
       </c>
       <c r="M67" s="5" t="n"/>
-      <c r="N67" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N67" s="2" t="n"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
         <is>
           <t>54a12a4b69702db648a6fb01</t>
         </is>
@@ -4778,17 +4894,18 @@
         </is>
       </c>
       <c r="M68" s="5" t="n"/>
-      <c r="N68" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N68" s="2" t="n"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
         <is>
           <t>5ef45bdd33527e0184a69242</t>
         </is>
@@ -4843,15 +4960,20 @@
       <c r="M69" s="5" t="n"/>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Acquired by Victors Home Solutions (Dec 2024). Phone is a NJ 856 area code despite PA address.</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
         <is>
           <t>5e55e4cc46c72000019e6c31</t>
         </is>
@@ -4904,17 +5026,18 @@
         </is>
       </c>
       <c r="M70" s="5" t="n"/>
-      <c r="N70" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N70" s="2" t="n"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
         <is>
           <t>5d09a775a3ae619a7ab0eb91</t>
         </is>
@@ -4967,17 +5090,18 @@
         </is>
       </c>
       <c r="M71" s="5" t="n"/>
-      <c r="N71" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N71" s="2" t="n"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
         <is>
           <t>66e7d882edbc350001d96b05</t>
         </is>
@@ -5030,17 +5154,18 @@
         </is>
       </c>
       <c r="M72" s="5" t="n"/>
-      <c r="N72" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N72" s="2" t="n"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
         <is>
           <t>5e79cc88d02d2900c2e8bb64</t>
         </is>
@@ -5093,17 +5218,18 @@
         </is>
       </c>
       <c r="M73" s="5" t="n"/>
-      <c r="N73" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N73" s="2" t="n"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
         <is>
           <t>5da3a36d04829100014f82c3</t>
         </is>
@@ -5156,17 +5282,18 @@
         </is>
       </c>
       <c r="M74" s="5" t="n"/>
-      <c r="N74" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N74" s="2" t="n"/>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
         <is>
           <t>61eb850584da410001ca3aa9</t>
         </is>
@@ -5219,17 +5346,18 @@
         </is>
       </c>
       <c r="M75" s="5" t="n"/>
-      <c r="N75" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N75" s="2" t="n"/>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
         <is>
           <t>55e7ea2bf3e5bb1b070003ae</t>
         </is>
@@ -5282,17 +5410,18 @@
         </is>
       </c>
       <c r="M76" s="5" t="n"/>
-      <c r="N76" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N76" s="2" t="n"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
         <is>
           <t>6727d6f489fe3607d3244c13</t>
         </is>
@@ -5345,17 +5474,18 @@
         </is>
       </c>
       <c r="M77" s="5" t="n"/>
-      <c r="N77" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N77" s="2" t="n"/>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
         <is>
           <t>5f4152d9b3305e00013404db</t>
         </is>
@@ -5408,17 +5538,18 @@
         </is>
       </c>
       <c r="M78" s="5" t="n"/>
-      <c r="N78" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N78" s="2" t="n"/>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
         <is>
           <t>54a1a5cf7468694012b79104</t>
         </is>
@@ -5473,15 +5604,20 @@
       <c r="M79" s="5" t="n"/>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Apollo keyword list is polluted with unrelated e-commerce/Lazada terms.</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
         <is>
           <t>5da65c46e03360000162126d</t>
         </is>
@@ -5536,15 +5672,20 @@
       <c r="M80" s="5" t="n"/>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Manufacturer's rep firm, not a roofing contractor.</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
         <is>
           <t>54a1abc2746869586066a106</t>
         </is>
@@ -5597,17 +5738,18 @@
         </is>
       </c>
       <c r="M81" s="5" t="n"/>
-      <c r="N81" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N81" s="2" t="n"/>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
         <is>
           <t>5e56be869f95ad0001367773</t>
         </is>
@@ -5660,17 +5802,18 @@
         </is>
       </c>
       <c r="M82" s="5" t="n"/>
-      <c r="N82" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N82" s="2" t="n"/>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
         <is>
           <t>5b87022e324d445cc0323c57</t>
         </is>
@@ -5719,17 +5862,18 @@
         </is>
       </c>
       <c r="M83" s="5" t="n"/>
-      <c r="N83" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N83" s="2" t="n"/>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
         <is>
           <t>5da39bd6dabf880001b3a966</t>
         </is>
@@ -5784,15 +5928,20 @@
       <c r="M84" s="5" t="n"/>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>HVAC coatings specialist; acquired by Nationwide Cooling Group (Mar 2026).</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
         <is>
           <t>5ed341e3f2ab0d00011079ca</t>
         </is>
@@ -5845,17 +5994,18 @@
         </is>
       </c>
       <c r="M85" s="5" t="n"/>
-      <c r="N85" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N85" s="2" t="n"/>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
         <is>
           <t>5e5606e3e36a770001bec1fe</t>
         </is>
@@ -5910,15 +6060,20 @@
       <c r="M86" s="5" t="n"/>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Consulting engineering firm, not a trade contractor.</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
         <is>
           <t>54a126cc69702da220c50300</t>
         </is>
@@ -5973,15 +6128,20 @@
       <c r="M87" s="5" t="n"/>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Staffing agency, not a contractor.</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
         <is>
           <t>54a11d0569702d8aa19fd000</t>
         </is>
@@ -6036,15 +6196,20 @@
       <c r="M88" s="5" t="n"/>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Manufacturers' rep agency, not a contractor.</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
         <is>
           <t>55ebbfc4f3e5bb61e2001f84</t>
         </is>
@@ -6099,15 +6264,20 @@
       <c r="M89" s="5" t="n"/>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Manufacturers' rep agency, not a contractor.</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
         <is>
           <t>5fc9a72a684f7800013fbb64</t>
         </is>
@@ -6162,22 +6332,27 @@
       <c r="M90" s="5" t="n"/>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Energy consulting firm, not a contractor.</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T02:29:30+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
           <t>5a9ee960a6da98d98c70c9f2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P90"/>
+  <autoFilter ref="A1:Q90"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
